--- a/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_제조기술1팀_입력_2026.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
